--- a/artfynd/A 63185-2023 artfynd.xlsx
+++ b/artfynd/A 63185-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -780,6 +780,323 @@
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>135236028</v>
+      </c>
+      <c r="B3" t="n">
+        <v>102496</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>221317</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Gullklöver</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Trifolium aureum</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Pollich</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Skogstrp O om , Srm</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>590915</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6541307</v>
+      </c>
+      <c r="S3" t="n">
+        <v>50</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Flen</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Vadsbro</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2026-07-18</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2026-07-18</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF3" t="inlineStr"/>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>Ruderatmark</t>
+        </is>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Rolf Olsson</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Rolf Olsson</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>135236145</v>
+      </c>
+      <c r="B4" t="n">
+        <v>98277</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>222736</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Majbräken</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Athyrium filix-femina</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(L.) Roth</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Skogstorp O om , Srm</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>590915</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6541307</v>
+      </c>
+      <c r="S4" t="n">
+        <v>50</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Flen</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Vadsbro</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2026-07-18</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2026-07-18</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF4" t="inlineStr"/>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH4" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Rolf Olsson</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Rolf Olsson</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>135235783</v>
+      </c>
+      <c r="B5" t="n">
+        <v>103908</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>225103</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Vanlig sälg</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Salix caprea subsp. caprea</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr"/>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Skogstrp O om , Srm</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>590915</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6541307</v>
+      </c>
+      <c r="S5" t="n">
+        <v>50</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Flen</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Vadsbro</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2026-07-18</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2026-07-18</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF5" t="inlineStr"/>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Rolf Olsson</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Rolf Olsson</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 63185-2023 artfynd.xlsx
+++ b/artfynd/A 63185-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AZ5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -779,6 +784,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95856792</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -886,6 +896,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135236028</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -993,6 +1008,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135236145</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1096,8 +1116,19 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135235783</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/artfynd/A 63185-2023 artfynd.xlsx
+++ b/artfynd/A 63185-2023 artfynd.xlsx
@@ -795,7 +795,7 @@
         <v>135236028</v>
       </c>
       <c r="B3" t="n">
-        <v>102496</v>
+        <v>102546</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>135236145</v>
       </c>
       <c r="B4" t="n">
-        <v>98277</v>
+        <v>98321</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>135235783</v>
       </c>
       <c r="B5" t="n">
-        <v>103908</v>
+        <v>103959</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 63185-2023 artfynd.xlsx
+++ b/artfynd/A 63185-2023 artfynd.xlsx
@@ -795,7 +795,7 @@
         <v>135236028</v>
       </c>
       <c r="B3" t="n">
-        <v>102546</v>
+        <v>102573</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>135236145</v>
       </c>
       <c r="B4" t="n">
-        <v>98321</v>
+        <v>98348</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>135235783</v>
       </c>
       <c r="B5" t="n">
-        <v>103959</v>
+        <v>103986</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 63185-2023 artfynd.xlsx
+++ b/artfynd/A 63185-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ3"/>
+  <dimension ref="A1:AZ5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -792,30 +792,34 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>135235783</v>
+        <v>135236028</v>
       </c>
       <c r="B3" t="n">
-        <v>103986</v>
+        <v>102578</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>225103</v>
+        <v>221317</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vanlig sälg</t>
+          <t>Gullklöver</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Salix caprea subsp. caprea</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr"/>
+          <t>Trifolium aureum</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Pollich</t>
+        </is>
+      </c>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
@@ -875,9 +879,9 @@
       <c r="AG3" t="b">
         <v>0</v>
       </c>
-      <c r="AH3" t="inlineStr">
-        <is>
-          <t>Skogsmark</t>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>Ruderatmark</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -893,6 +897,226 @@
       </c>
       <c r="AY3" t="inlineStr"/>
       <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135236028</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>135236145</v>
+      </c>
+      <c r="B4" t="n">
+        <v>98353</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>222736</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Majbräken</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Athyrium filix-femina</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(L.) Roth</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Skogstorp O om , Srm</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>590915</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6541307</v>
+      </c>
+      <c r="S4" t="n">
+        <v>50</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Flen</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Vadsbro</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2026-07-18</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2026-07-18</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF4" t="inlineStr"/>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH4" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Rolf Olsson</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Rolf Olsson</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135236145</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>135235783</v>
+      </c>
+      <c r="B5" t="n">
+        <v>103991</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>225103</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Vanlig sälg</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Salix caprea subsp. caprea</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr"/>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Skogstrp O om , Srm</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>590915</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6541307</v>
+      </c>
+      <c r="S5" t="n">
+        <v>50</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Flen</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Vadsbro</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2026-07-18</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2026-07-18</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF5" t="inlineStr"/>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Rolf Olsson</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Rolf Olsson</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/135235783</t>
         </is>
@@ -902,6 +1126,8 @@
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 63185-2023 artfynd.xlsx
+++ b/artfynd/A 63185-2023 artfynd.xlsx
@@ -795,7 +795,7 @@
         <v>135236028</v>
       </c>
       <c r="B3" t="n">
-        <v>102578</v>
+        <v>102580</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>135236145</v>
       </c>
       <c r="B4" t="n">
-        <v>98353</v>
+        <v>98355</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>135235783</v>
       </c>
       <c r="B5" t="n">
-        <v>103991</v>
+        <v>103993</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
